--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853388</v>
+        <v>121853389</v>
       </c>
       <c r="B2" t="n">
-        <v>94778</v>
+        <v>95660</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533413</v>
+        <v>533400</v>
       </c>
       <c r="R2" t="n">
-        <v>6672452</v>
+        <v>6672453</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853389</v>
+        <v>121853388</v>
       </c>
       <c r="B3" t="n">
-        <v>95660</v>
+        <v>94778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533400</v>
+        <v>533413</v>
       </c>
       <c r="R3" t="n">
-        <v>6672453</v>
+        <v>6672452</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853389</v>
+        <v>121853388</v>
       </c>
       <c r="B2" t="n">
-        <v>95660</v>
+        <v>94778</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533400</v>
+        <v>533413</v>
       </c>
       <c r="R2" t="n">
-        <v>6672453</v>
+        <v>6672452</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853388</v>
+        <v>121853389</v>
       </c>
       <c r="B3" t="n">
-        <v>94778</v>
+        <v>95660</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533413</v>
+        <v>533400</v>
       </c>
       <c r="R3" t="n">
-        <v>6672452</v>
+        <v>6672453</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853389</v>
       </c>
       <c r="B2" t="n">
-        <v>95660</v>
+        <v>95678</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>121853388</v>
       </c>
       <c r="B3" t="n">
-        <v>94778</v>
+        <v>94796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853389</v>
+        <v>121853388</v>
       </c>
       <c r="B2" t="n">
-        <v>95678</v>
+        <v>94798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533400</v>
+        <v>533413</v>
       </c>
       <c r="R2" t="n">
-        <v>6672453</v>
+        <v>6672452</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853388</v>
+        <v>121853389</v>
       </c>
       <c r="B3" t="n">
-        <v>94796</v>
+        <v>95680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533413</v>
+        <v>533400</v>
       </c>
       <c r="R3" t="n">
-        <v>6672452</v>
+        <v>6672453</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853388</v>
       </c>
       <c r="B2" t="n">
-        <v>94798</v>
+        <v>94805</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>121853389</v>
       </c>
       <c r="B3" t="n">
-        <v>95680</v>
+        <v>95687</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121853388</v>
       </c>
       <c r="B2" t="n">
-        <v>94805</v>
+        <v>94814</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>121853389</v>
       </c>
       <c r="B3" t="n">
-        <v>95687</v>
+        <v>95696</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121853388</v>
+        <v>121853389</v>
       </c>
       <c r="B2" t="n">
-        <v>94840</v>
+        <v>95722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533413</v>
+        <v>533400</v>
       </c>
       <c r="R2" t="n">
-        <v>6672452</v>
+        <v>6672453</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -774,7 +774,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>tallstubbe</t>
+          <t>tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121853389</v>
+        <v>121853388</v>
       </c>
       <c r="B3" t="n">
-        <v>95722</v>
+        <v>94840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>533400</v>
+        <v>533413</v>
       </c>
       <c r="R3" t="n">
-        <v>6672453</v>
+        <v>6672452</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>tallstubbe</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121853389</v>
       </c>
       <c r="B2" t="n">
-        <v>95722</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,12 +790,7 @@
         <v>121853388</v>
       </c>
       <c r="B3" t="n">
-        <v>94840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57246-2021 artfynd.xlsx
+++ b/artfynd/A 57246-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853389</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,8 +906,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121853388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>